--- a/data/trans_orig/IP09B02-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP09B02-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2007 (tasa de respuesta: 98,55%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2007 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -768,7 +768,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>8380</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13649</t>
+          <t>13585</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>17321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,7%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>50,56%</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12768</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,27%</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>8748</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,42%</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>64,95%</t>
         </is>
       </c>
     </row>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>3119</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>585</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>568</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>56,03%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>8260</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>13769</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14353</t>
+          <t>15036</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21471</t>
+          <t>21959</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>88,36%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3380</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>9815</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>39,49%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>9049</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>14358</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20801</t>
+          <t>20876</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>20650</t>
+          <t>20473</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28731</t>
+          <t>28900</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2450</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7388</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>13880</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>33568</t>
+          <t>33479</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44653</t>
+          <t>44264</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>61625</t>
+          <t>61042</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>72284</t>
+          <t>72400</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>98650</t>
+          <t>98413</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>114986</t>
+          <t>114016</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>82,8%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>11310</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>22095</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>20506</t>
+          <t>21089</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22719</t>
+          <t>23689</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>39055</t>
+          <t>39292</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2012 (tasa de respuesta: 97,74%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2012 (tasa de respuesta: 97,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7607</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>12854</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>14361</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>17455</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25941</t>
+          <t>25832</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>2282</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13777</t>
+          <t>13849</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8822</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17967</t>
+          <t>17797</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>78,51%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,73%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4871</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12161</t>
+          <t>12304</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>54,28%</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7171</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13368</t>
+          <t>13353</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,02%</t>
         </is>
       </c>
     </row>
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>869</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>59,61%</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>13189</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>44,11%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>749</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>716</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>742</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9331</t>
+          <t>9077</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>61,0%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>10926</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9360</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>15505</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17070</t>
+          <t>16624</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25027</t>
+          <t>25008</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,81%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>8068</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12768</t>
+          <t>13214</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10423</t>
+          <t>9992</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>13955</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11777</t>
+          <t>11533</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21735</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>52,57%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>15071</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15770</t>
+          <t>15909</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18861</t>
+          <t>19253</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28819</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,59%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43961</t>
+          <t>44459</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>58425</t>
+          <t>58200</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>53943</t>
+          <t>54405</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>70547</t>
+          <t>69358</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>102383</t>
+          <t>102009</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>123457</t>
+          <t>122446</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>24042</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38281</t>
+          <t>37783</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27737</t>
+          <t>28926</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44341</t>
+          <t>43879</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>57070</t>
+          <t>58081</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>78144</t>
+          <t>78518</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2016 (tasa de respuesta: 99,32%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2016 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7696</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13787</t>
+          <t>13929</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>853</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5864</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8212</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1335</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>74,74%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>82,07%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>63,88%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11577</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>17433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,27%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1235</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6494</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7115</t>
+          <t>7702</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>798</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>39,57%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6758</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9519</t>
+          <t>9257</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14585</t>
+          <t>14521</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6751</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11646</t>
+          <t>11098</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>66,89%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11376</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>71,01%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11620</t>
+          <t>11651</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,79%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10468</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>65,39%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18596</t>
+          <t>18533</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>29516</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21865</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33701</t>
+          <t>34242</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>44075</t>
+          <t>45337</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>60958</t>
+          <t>61043</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,93%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>16870</t>
+          <t>17607</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28527</t>
+          <t>28590</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17746</t>
+          <t>17205</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29582</t>
+          <t>28699</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>37612</t>
+          <t>37527</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54495</t>
+          <t>53233</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si dicha enfermedad o dolencia continuada le ha afectado para realizar actividades de ocio como pasear, ir al cine, hacer deporte, etc en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10191</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22931</t>
+          <t>22971</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -10787,7 +10787,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7307</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1597</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,29%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2173</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7341</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10557</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>63,0%</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11388,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9338</t>
+          <t>9640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>746</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>6058</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>38,59%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13733</t>
+          <t>14036</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>21746</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19020</t>
+          <t>18815</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29834</t>
+          <t>29689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>456</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8469</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1654</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>12673</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>40,25%</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12227,7 +12227,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2516</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>437</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>48,9%</t>
         </is>
       </c>
     </row>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6344</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>80,36%</t>
         </is>
       </c>
     </row>
@@ -12535,7 +12535,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7759</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>60,93%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>10046</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12704</t>
+          <t>13067</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19483</t>
+          <t>19923</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21156</t>
+          <t>21471</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29021</t>
+          <t>28858</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>382</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>11057</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>33,99%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13047</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>80,83%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>4713</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>6766</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>59,25%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>45687</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56624</t>
+          <t>56596</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>64030</t>
+          <t>63923</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>82179</t>
+          <t>82207</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>113774</t>
+          <t>114571</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>134739</t>
+          <t>135763</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,51%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6924</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>18520</t>
+          <t>17861</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>16822</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34999</t>
+          <t>35106</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>27839</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>48804</t>
+          <t>48007</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
